--- a/Data_Toko.xlsx
+++ b/Data_Toko.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Toko_Intan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A3633C-7F6C-4FB3-B8CE-D0C63DDEE152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78801258-6DEA-45F8-9F81-94DBB7726062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{C301A6B1-2A80-44BD-B04E-4ECE22086F81}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18930" windowHeight="9240" xr2:uid="{C301A6B1-2A80-44BD-B04E-4ECE22086F81}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>id</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>deskripsi</t>
-  </si>
-  <si>
-    <t>waAdmin</t>
   </si>
   <si>
     <t>Legging Hitam Premium</t>
@@ -460,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640EF6BD-F493-4D6F-80DF-145CCB18A00D}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
@@ -473,7 +470,7 @@
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,13 +492,10 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>8</v>
       </c>
       <c r="C2" s="1">
         <v>65000</v>
@@ -510,21 +504,18 @@
         <v>95000</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2">
-        <v>6281234567890</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>75000</v>
@@ -533,16 +524,13 @@
         <v>110000</v>
       </c>
       <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
       <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>6281234567890</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Toko.xlsx
+++ b/Data_Toko.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Toko_Intan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78801258-6DEA-45F8-9F81-94DBB7726062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CD849B-84EB-4F9F-A31E-A62472D3D147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1560" windowWidth="18930" windowHeight="9240" xr2:uid="{C301A6B1-2A80-44BD-B04E-4ECE22086F81}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="15">
   <si>
     <t>id</t>
   </si>
@@ -457,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640EF6BD-F493-4D6F-80DF-145CCB18A00D}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
@@ -533,6 +533,186 @@
         <v>13</v>
       </c>
     </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1">
+        <v>85000</v>
+      </c>
+      <c r="D4" s="1">
+        <v>125000</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1">
+        <v>95000</v>
+      </c>
+      <c r="D5" s="1">
+        <v>140000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1">
+        <v>105000</v>
+      </c>
+      <c r="D6" s="1">
+        <v>155000</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1">
+        <v>115000</v>
+      </c>
+      <c r="D7" s="1">
+        <v>170000</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1">
+        <v>125000</v>
+      </c>
+      <c r="D8" s="1">
+        <v>185000</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1">
+        <v>135000</v>
+      </c>
+      <c r="D9" s="1">
+        <v>200000</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1">
+        <v>145000</v>
+      </c>
+      <c r="D10" s="1">
+        <v>215000</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1">
+        <v>155000</v>
+      </c>
+      <c r="D11" s="1">
+        <v>230000</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1">
+        <v>165000</v>
+      </c>
+      <c r="D12" s="1">
+        <v>245000</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
